--- a/Server.xlsx
+++ b/Server.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/13a0fd42d83c08bf/Documents/Cursos/ILLINOIS/IE_421_High_Frequency_Trading/LinuxVM/LLM_Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC1D7A16-F068-0A44-AE69-4DDA8F3CDE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{CC1D7A16-F068-0A44-AE69-4DDA8F3CDE39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15AB10C5-2C35-954A-9E02-A66CA17D6CBC}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="17160" xr2:uid="{344EA844-2196-F949-BB92-859D93BACC5B}"/>
+    <workbookView xWindow="680" yWindow="660" windowWidth="28040" windowHeight="17160" activeTab="2" xr2:uid="{344EA844-2196-F949-BB92-859D93BACC5B}"/>
   </bookViews>
   <sheets>
     <sheet name="Servers" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="384">
   <si>
     <t>Server_ID</t>
   </si>
@@ -199,9 +199,6 @@
     <t>Default_Value</t>
   </si>
   <si>
-    <t>Manual_Page</t>
-  </si>
-  <si>
     <t>Manual_Description</t>
   </si>
   <si>
@@ -830,9 +827,6 @@
   </si>
   <si>
     <t>Advanced → Boot Feature</t>
-  </si>
-  <si>
-    <t>Chapter 4</t>
   </si>
   <si>
     <t>Use this feature to select the screen display between the Power-on Self Test (POST) messages and the OEM logo upon bootup. The options are Disabled and Enabled.</t>
@@ -1258,13 +1252,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1607,6 +1599,8 @@
     <col min="3" max="3" width="19.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="60.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="61" bestFit="1" customWidth="1"/>
   </cols>
@@ -1820,13 +1814,13 @@
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>27</v>
@@ -1852,13 +1846,13 @@
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>27</v>
@@ -1884,13 +1878,13 @@
         <v>33</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>385</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>34</v>
@@ -1921,6 +1915,7 @@
   <cols>
     <col min="1" max="1" width="19.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="61" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -2003,18 +1998,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CF5F156-EF62-0649-9161-77FDD0D0C561}">
-  <dimension ref="A1:S82"/>
+  <dimension ref="A1:R82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="48.33203125" customWidth="1"/>
+    <col min="5" max="5" width="48.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -2034,10 +2028,10 @@
         <v>53</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>55</v>
@@ -2069,34 +2063,31 @@
       <c r="R1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="E2" s="4">
-        <v>46205</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>219</v>
+        <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>15</v>
@@ -2128,34 +2119,31 @@
       <c r="R2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E3" s="4">
-        <v>46205</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>221</v>
+        <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>15</v>
@@ -2187,34 +2175,31 @@
       <c r="R3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E4" s="4">
-        <v>46205</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>223</v>
+        <v>68</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>15</v>
@@ -2246,34 +2231,31 @@
       <c r="R4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E5" s="4">
-        <v>46205</v>
-      </c>
       <c r="F5" s="2" t="s">
-        <v>225</v>
+        <v>68</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>15</v>
@@ -2305,34 +2287,31 @@
       <c r="R5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E6" s="4">
-        <v>46205</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>228</v>
+        <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>15</v>
@@ -2364,34 +2343,31 @@
       <c r="R6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E7" s="4">
-        <v>46205</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>230</v>
+        <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>15</v>
@@ -2423,55 +2399,52 @@
       <c r="R7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="E8" s="4">
-        <v>46206</v>
-      </c>
       <c r="F8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>233</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>235</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>236</v>
+        <v>14</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>14</v>
+        <v>236</v>
       </c>
       <c r="N8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>238</v>
@@ -2482,93 +2455,87 @@
       <c r="R8" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="S8" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E9" s="4">
-        <v>46206</v>
-      </c>
       <c r="F9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>244</v>
+        <v>132</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>14</v>
+        <v>244</v>
       </c>
       <c r="N9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>246</v>
       </c>
       <c r="Q9" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="R9" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="R9" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E10" s="4">
-        <v>46206</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>182</v>
+        <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>15</v>
@@ -2600,34 +2567,31 @@
       <c r="R10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S10" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="E11" s="4">
-        <v>46206</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>15</v>
@@ -2659,34 +2623,31 @@
       <c r="R11" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S11" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="E12" s="4">
-        <v>46206</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>188</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>15</v>
@@ -2718,34 +2679,31 @@
       <c r="R12" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S12" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E13" s="4">
-        <v>46206</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>190</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>15</v>
@@ -2777,34 +2735,31 @@
       <c r="R13" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S13" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="E14" s="4">
-        <v>46206</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>251</v>
+        <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>15</v>
@@ -2836,34 +2791,31 @@
       <c r="R14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S14" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" s="4">
-        <v>46206</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>253</v>
+        <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>15</v>
@@ -2895,58 +2847,55 @@
       <c r="R15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S15" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E16" s="4">
-        <v>46206</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>254</v>
-      </c>
       <c r="G16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="I16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="J16" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="K16" s="2" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>72</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>175</v>
+        <v>88</v>
       </c>
       <c r="Q16" s="2" t="s">
         <v>89</v>
@@ -2954,49 +2903,46 @@
       <c r="R16" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="S16" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" s="4">
-        <v>46206</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="J17" s="2" t="s">
-        <v>256</v>
-      </c>
       <c r="K17" s="2" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>77</v>
@@ -3011,95 +2957,89 @@
         <v>80</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" s="4">
-        <v>46206</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="I18" s="2" t="s">
-        <v>83</v>
+        <v>175</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>176</v>
+        <v>75</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="N18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O18" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>85</v>
       </c>
       <c r="Q18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="R18" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="R18" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" s="4">
-        <v>46206</v>
+      <c r="E19" s="2" t="s">
+        <v>257</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>258</v>
+        <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>95</v>
@@ -3108,13 +3048,13 @@
         <v>96</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>98</v>
@@ -3131,55 +3071,52 @@
       <c r="R19" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="S19" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E20" s="4">
-        <v>46206</v>
-      </c>
       <c r="F20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>107</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="N20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O20" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>110</v>
@@ -3190,506 +3127,479 @@
       <c r="R20" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="S20" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E21" s="4">
-        <v>46206</v>
-      </c>
       <c r="F21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>116</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>14</v>
+        <v>117</v>
       </c>
       <c r="N21" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="O21" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="O21" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="P21" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="Q21" s="2" t="s">
         <v>111</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S21" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E22" s="4">
-        <v>46206</v>
-      </c>
       <c r="F22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>124</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>125</v>
+        <v>14</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>14</v>
+        <v>125</v>
       </c>
       <c r="N22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O22" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>127</v>
       </c>
       <c r="Q22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R22" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="R22" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S22" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E23" s="4">
-        <v>46206</v>
-      </c>
       <c r="F23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>132</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="N23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O23" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>135</v>
       </c>
       <c r="Q23" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R23" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="R23" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S23" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="4">
-        <v>46206</v>
-      </c>
       <c r="F24" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>140</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>141</v>
+        <v>14</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>14</v>
+        <v>141</v>
       </c>
       <c r="N24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="P24" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="O24" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="Q24" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R24" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="R24" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E25" s="4">
-        <v>46206</v>
-      </c>
       <c r="F25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>147</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>148</v>
+        <v>14</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>14</v>
+        <v>148</v>
       </c>
       <c r="N25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="P25" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="O25" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="Q25" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R25" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="R25" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S25" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E26" s="4">
-        <v>46206</v>
-      </c>
       <c r="F26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="J26" s="2" t="s">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="N26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O26" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>156</v>
       </c>
       <c r="Q26" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R26" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="R26" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S26" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E27" s="4">
-        <v>46206</v>
-      </c>
       <c r="F27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="J27" s="2" t="s">
-        <v>161</v>
+        <v>75</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="N27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O27" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="O27" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="P27" s="2" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="Q27" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R27" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="R27" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S27" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E28" s="4">
-        <v>46206</v>
-      </c>
       <c r="F28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="J28" s="2" t="s">
-        <v>166</v>
+        <v>75</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>14</v>
+        <v>166</v>
       </c>
       <c r="N28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="P28" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="O28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="Q28" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R28" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="R28" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S28" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D29" s="2">
         <v>24</v>
       </c>
-      <c r="E29" s="4">
-        <v>46206</v>
+      <c r="E29" s="2" t="s">
+        <v>208</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>209</v>
+        <v>68</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>15</v>
@@ -3721,34 +3631,31 @@
       <c r="R29" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S29" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E30" s="4">
-        <v>46206</v>
-      </c>
       <c r="F30" s="2" t="s">
-        <v>260</v>
+        <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>15</v>
@@ -3780,34 +3687,31 @@
       <c r="R30" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S30" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D31" s="2" t="s">
+      <c r="F31" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E31" s="4">
-        <v>46206</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>192</v>
-      </c>
       <c r="G31" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>15</v>
@@ -3839,34 +3743,31 @@
       <c r="R31" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S31" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E32" s="4">
-        <v>46206</v>
-      </c>
       <c r="F32" s="2" t="s">
-        <v>213</v>
+        <v>68</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>15</v>
@@ -3898,34 +3799,31 @@
       <c r="R32" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S32" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E33" s="4">
-        <v>46206</v>
-      </c>
       <c r="F33" s="2" t="s">
-        <v>215</v>
+        <v>68</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>15</v>
@@ -3957,34 +3855,31 @@
       <c r="R33" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S33" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E34" s="4">
-        <v>46206</v>
-      </c>
       <c r="F34" s="2" t="s">
-        <v>195</v>
+        <v>68</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>15</v>
@@ -4016,34 +3911,31 @@
       <c r="R34" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S34" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="D35" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E35" s="4">
-        <v>46206</v>
-      </c>
       <c r="F35" s="2" t="s">
-        <v>198</v>
+        <v>68</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>15</v>
@@ -4075,34 +3967,31 @@
       <c r="R35" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S35" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E36" s="4">
-        <v>46206</v>
-      </c>
       <c r="F36" s="2" t="s">
-        <v>201</v>
+        <v>68</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>15</v>
@@ -4134,34 +4023,31 @@
       <c r="R36" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S36" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D37" s="2" t="s">
+      <c r="E37" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="E37" s="4">
-        <v>46206</v>
-      </c>
       <c r="F37" s="2" t="s">
-        <v>204</v>
+        <v>68</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>15</v>
@@ -4193,34 +4079,31 @@
       <c r="R37" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S37" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D38" s="2" t="s">
+      <c r="E38" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E38" s="4">
-        <v>46206</v>
-      </c>
       <c r="F38" s="2" t="s">
-        <v>207</v>
+        <v>68</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>69</v>
+        <v>173</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>15</v>
@@ -4252,34 +4135,31 @@
       <c r="R38" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E39" s="2" t="s">
+      <c r="F39" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F39" s="2" t="s">
-        <v>264</v>
-      </c>
       <c r="G39" s="2" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>15</v>
@@ -4311,34 +4191,31 @@
       <c r="R39" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S39" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E40" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F40" s="2" t="s">
-        <v>267</v>
-      </c>
       <c r="G40" s="2" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>15</v>
@@ -4370,34 +4247,31 @@
       <c r="R40" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S40" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E41" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F41" s="2" t="s">
-        <v>269</v>
-      </c>
       <c r="G41" s="2" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>15</v>
@@ -4429,34 +4303,31 @@
       <c r="R41" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S41" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E42" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F42" s="2" t="s">
-        <v>271</v>
-      </c>
       <c r="G42" s="2" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>15</v>
@@ -4488,34 +4359,31 @@
       <c r="R42" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S42" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E43" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F43" s="2" t="s">
-        <v>273</v>
-      </c>
       <c r="G43" s="2" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>15</v>
@@ -4547,34 +4415,31 @@
       <c r="R43" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S43" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E44" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F44" s="2" t="s">
-        <v>275</v>
-      </c>
       <c r="G44" s="2" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>15</v>
@@ -4606,34 +4471,31 @@
       <c r="R44" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S44" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="D45" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E45" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F45" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F45" s="2" t="s">
-        <v>276</v>
-      </c>
       <c r="G45" s="2" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>15</v>
@@ -4665,34 +4527,31 @@
       <c r="R45" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S45" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="E46" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F46" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F46" s="2" t="s">
-        <v>277</v>
-      </c>
       <c r="G46" s="2" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>15</v>
@@ -4724,34 +4583,31 @@
       <c r="R46" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S46" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E47" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F47" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F47" s="2" t="s">
-        <v>279</v>
-      </c>
       <c r="G47" s="2" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>15</v>
@@ -4783,152 +4639,143 @@
       <c r="R47" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S47" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I48" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="J48" s="2" t="s">
-        <v>282</v>
+        <v>96</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>98</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>99</v>
+        <v>281</v>
       </c>
       <c r="P48" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q48" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="Q48" s="2" t="s">
+      <c r="R48" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="R48" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="S48" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I49" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="J49" s="2" t="s">
-        <v>289</v>
+        <v>124</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>125</v>
+        <v>14</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>14</v>
+        <v>288</v>
       </c>
       <c r="N49" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R49" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="O49" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P49" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q49" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="R49" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S49" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E50" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>294</v>
-      </c>
       <c r="G50" s="2" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>15</v>
@@ -4960,34 +4807,31 @@
       <c r="R50" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S50" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E51" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F51" s="2" t="s">
-        <v>296</v>
-      </c>
       <c r="G51" s="2" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>15</v>
@@ -5019,93 +4863,87 @@
       <c r="R51" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S51" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I52" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="J52" s="2" t="s">
-        <v>299</v>
+        <v>147</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>148</v>
+        <v>14</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>14</v>
+        <v>298</v>
       </c>
       <c r="N52" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O52" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q52" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R52" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="O52" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="P52" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q52" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="R52" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S52" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E53" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>304</v>
-      </c>
       <c r="G53" s="2" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>15</v>
@@ -5137,34 +4975,31 @@
       <c r="R53" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S53" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E54" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F54" s="2" t="s">
-        <v>306</v>
-      </c>
       <c r="G54" s="2" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>15</v>
@@ -5196,34 +5031,31 @@
       <c r="R54" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S54" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B55" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E55" s="2" t="s">
+      <c r="F55" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F55" s="2" t="s">
-        <v>309</v>
-      </c>
       <c r="G55" s="2" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>15</v>
@@ -5255,34 +5087,31 @@
       <c r="R55" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S55" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B56" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="E56" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="E56" s="2" t="s">
+      <c r="F56" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F56" s="2" t="s">
-        <v>313</v>
-      </c>
       <c r="G56" s="2" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>15</v>
@@ -5314,34 +5143,31 @@
       <c r="R56" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S56" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E57" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>315</v>
-      </c>
       <c r="G57" s="2" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>15</v>
@@ -5373,34 +5199,31 @@
       <c r="R57" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S57" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E58" s="2" t="s">
+      <c r="F58" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F58" s="2" t="s">
-        <v>318</v>
-      </c>
       <c r="G58" s="2" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>15</v>
@@ -5432,34 +5255,31 @@
       <c r="R58" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S58" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E59" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F59" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F59" s="2" t="s">
-        <v>318</v>
-      </c>
       <c r="G59" s="2" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>15</v>
@@ -5491,34 +5311,31 @@
       <c r="R59" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S59" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E60" s="2" t="s">
+      <c r="F60" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F60" s="2" t="s">
-        <v>322</v>
-      </c>
       <c r="G60" s="2" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>15</v>
@@ -5550,34 +5367,31 @@
       <c r="R60" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S60" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E61" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F61" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F61" s="2" t="s">
-        <v>324</v>
-      </c>
       <c r="G61" s="2" t="s">
-        <v>265</v>
+        <v>173</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>15</v>
@@ -5609,34 +5423,31 @@
       <c r="R61" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S61" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>263</v>
+        <v>323</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>326</v>
+        <v>173</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>15</v>
@@ -5668,34 +5479,31 @@
       <c r="R62" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S62" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>326</v>
+        <v>173</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>15</v>
@@ -5727,34 +5535,31 @@
       <c r="R63" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S63" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>263</v>
+        <v>326</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>326</v>
+        <v>173</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>15</v>
@@ -5786,34 +5591,31 @@
       <c r="R64" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S64" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>263</v>
+        <v>327</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>326</v>
+        <v>173</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>15</v>
@@ -5845,34 +5647,31 @@
       <c r="R65" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S65" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>263</v>
+        <v>328</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>326</v>
+        <v>173</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>15</v>
@@ -5904,34 +5703,31 @@
       <c r="R66" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S66" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>263</v>
+        <v>329</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>326</v>
+        <v>173</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>15</v>
@@ -5963,34 +5759,31 @@
       <c r="R67" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S67" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="D68" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>263</v>
+        <v>330</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>326</v>
+        <v>173</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>15</v>
@@ -6022,34 +5815,31 @@
       <c r="R68" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S68" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="E69" s="2" t="s">
-        <v>263</v>
+        <v>331</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>326</v>
+        <v>173</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>15</v>
@@ -6081,34 +5871,31 @@
       <c r="R69" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S69" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>263</v>
+        <v>332</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>326</v>
+        <v>173</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>15</v>
@@ -6140,329 +5927,311 @@
       <c r="R70" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S70" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B71" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I71" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="J71" s="2" t="s">
-        <v>299</v>
+        <v>147</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>148</v>
+        <v>14</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>14</v>
+        <v>298</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>300</v>
+        <v>77</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>178</v>
+        <v>299</v>
       </c>
       <c r="Q71" s="2" t="s">
-        <v>301</v>
+        <v>111</v>
       </c>
       <c r="R71" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S71" s="2" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.2">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B72" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I72" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="J72" s="2" t="s">
-        <v>339</v>
+        <v>132</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>14</v>
+        <v>244</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>245</v>
+        <v>77</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>78</v>
+        <v>338</v>
       </c>
       <c r="P72" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q72" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R72" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="Q72" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="R72" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S72" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I73" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="J73" s="2" t="s">
-        <v>345</v>
+        <v>140</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>141</v>
+        <v>14</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="N73" s="2" t="s">
         <v>98</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>99</v>
+        <v>344</v>
       </c>
       <c r="P73" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="Q73" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R73" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="Q73" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="R73" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S73" s="2" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>263</v>
+        <v>347</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>326</v>
+        <v>18</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>70</v>
+        <v>348</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>350</v>
+        <v>140</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>141</v>
+        <v>14</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="N74" s="2" t="s">
         <v>98</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>99</v>
+        <v>349</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="Q74" s="2" t="s">
-        <v>341</v>
+        <v>111</v>
       </c>
       <c r="R74" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S74" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B75" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I75" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="J75" s="2" t="s">
-        <v>289</v>
+        <v>124</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>125</v>
+        <v>14</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>14</v>
+        <v>288</v>
       </c>
       <c r="N75" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="O75" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="P75" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q75" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R75" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="O75" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P75" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q75" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="R75" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S75" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>263</v>
+        <v>352</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>354</v>
+        <v>324</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>326</v>
+        <v>173</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>15</v>
@@ -6494,34 +6263,31 @@
       <c r="R76" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S76" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>263</v>
+        <v>353</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>355</v>
+        <v>324</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>326</v>
+        <v>173</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>15</v>
@@ -6553,211 +6319,199 @@
       <c r="R77" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S77" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>263</v>
+        <v>354</v>
       </c>
       <c r="F78" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="J78" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="G78" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J78" s="2" t="s">
+      <c r="K78" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="K78" s="2" t="s">
+      <c r="L78" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M78" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="L78" s="2" t="s">
+      <c r="N78" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="O78" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="M78" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N78" s="2" t="s">
+      <c r="P78" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="O78" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="P78" s="2" t="s">
+      <c r="Q78" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="Q78" s="2" t="s">
+      <c r="R78" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="R78" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="S78" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>263</v>
+        <v>363</v>
       </c>
       <c r="F79" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="I79" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="G79" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>366</v>
-      </c>
       <c r="J79" s="2" t="s">
-        <v>367</v>
+        <v>75</v>
       </c>
       <c r="K79" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M79" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="L79" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="M79" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="N79" s="2" t="s">
         <v>77</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>78</v>
+        <v>366</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>368</v>
+        <v>79</v>
       </c>
       <c r="Q79" s="2" t="s">
         <v>80</v>
       </c>
       <c r="R79" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="S79" s="2" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H80" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F80" s="2" t="s">
+      <c r="I80" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="R80" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="P80" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="Q80" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="R80" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="D81" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E81" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="F81" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G81" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="G81" s="2" t="s">
-        <v>326</v>
-      </c>
       <c r="H81" s="2" t="s">
-        <v>174</v>
+        <v>15</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>15</v>
@@ -6789,67 +6543,61 @@
       <c r="R81" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="S81" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B82" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I82" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F82" s="2" t="s">
+      <c r="J82" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="M82" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="G82" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I82" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="J82" s="2" t="s">
+      <c r="N82" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="O82" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="K82" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="L82" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="M82" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="N82" s="2" t="s">
+      <c r="P82" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="O82" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="P82" s="2" t="s">
+      <c r="Q82" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="R82" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="Q82" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="R82" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S82" s="2" t="s">
-        <v>379</v>
       </c>
     </row>
   </sheetData>
